--- a/src/main/resources/static/docs/Requisito Funcional.xlsx
+++ b/src/main/resources/static/docs/Requisito Funcional.xlsx
@@ -8,12 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\prueba\uned-aplicacionweb\src\main\resources\static\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C15F2A35-F968-4799-B530-C3EFBF6081AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F05DDB59-4955-4A0E-9A47-D1BCE6CC3A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{874510E2-3812-42E8-85D1-73A795B0A65D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="6" xr2:uid="{874510E2-3812-42E8-85D1-73A795B0A65D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="FR_01-001" sheetId="1" r:id="rId1"/>
+    <sheet name="FR_01-002" sheetId="2" r:id="rId2"/>
+    <sheet name="FR_01_003" sheetId="3" r:id="rId3"/>
+    <sheet name="FR_01_004" sheetId="4" r:id="rId4"/>
+    <sheet name="FR_01_005" sheetId="5" r:id="rId5"/>
+    <sheet name="FR_01_006" sheetId="6" r:id="rId6"/>
+    <sheet name="FR_01_007" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="48">
   <si>
     <t>Código del requerimiento</t>
   </si>
@@ -48,134 +54,162 @@
     <t>Nombre</t>
   </si>
   <si>
-    <t>Relación de Declaraciones Mensuales de Entregas</t>
-  </si>
-  <si>
     <t>Propósito</t>
   </si>
   <si>
-    <t>Obtener las declaraciones mensuales presentadas en sus diferentes estados por el comprador.</t>
-  </si>
-  <si>
     <t>Descripción</t>
   </si>
   <si>
-    <t>Listado del histórico de Declaraciones mensuales presentadas por un comprador. Esta funcionalidad estará operativa para las 3 especies actualmente definidas: Vaca, Oveja y Cabra.</t>
-  </si>
-  <si>
     <t>Entrada</t>
   </si>
   <si>
-    <t>Acceso mediante menú a la opción a los perfiles autorizados</t>
-  </si>
-  <si>
     <t>Salida</t>
   </si>
   <si>
-    <r>
-      <t>Dependiendo del perfil: - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF14191A"/>
-        <rFont val="Noto Serif"/>
-        <family val="1"/>
-      </rPr>
-      <t>Gestor</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF14191A"/>
-        <rFont val="Noto Serif"/>
-        <family val="1"/>
-      </rPr>
-      <t>. Listado de las declaraciones presentadas por Compradores. - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF14191A"/>
-        <rFont val="Noto Serif"/>
-        <family val="1"/>
-      </rPr>
-      <t>Gestor Comunidad Autónoma</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF14191A"/>
-        <rFont val="Noto Serif"/>
-        <family val="1"/>
-      </rPr>
-      <t>. Listado de las declaraciones presentadas por Compradores de la Comunidad Autónoma adscrita al Gestor. - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF14191A"/>
-        <rFont val="Noto Serif"/>
-        <family val="1"/>
-      </rPr>
-      <t>Gestor Consulta Declaraciones</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF14191A"/>
-        <rFont val="Noto Serif"/>
-        <family val="1"/>
-      </rPr>
-      <t> - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF14191A"/>
-        <rFont val="Noto Serif"/>
-        <family val="1"/>
-      </rPr>
-      <t>Comprador.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF14191A"/>
-        <rFont val="Noto Serif"/>
-        <family val="1"/>
-      </rPr>
-      <t> Listado de las declaraciones presentadas por el Comprador. - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF14191A"/>
-        <rFont val="Noto Serif"/>
-        <family val="1"/>
-      </rPr>
-      <t>Productor.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF14191A"/>
-        <rFont val="Noto Serif"/>
-        <family val="1"/>
-      </rPr>
-      <t> Listado de las declaraciones en las que interviene el Productor.</t>
-    </r>
-  </si>
-  <si>
     <t>Prioridad</t>
   </si>
   <si>
     <t>Alta</t>
+  </si>
+  <si>
+    <t>Consulta de Cursos</t>
+  </si>
+  <si>
+    <t>Se mostrará en pantalla los cursos existentes de forma paginada en 3 categorías:
+1.- Cursos más populares (Cursos con mayor número de vistas)
+2.- Cursos mejor valororados (Cursos ordenados por mejor valoración media)
+3.- Cursos con mayor participación (Cursos ordenados por número de estudiantes inscritos)</t>
+  </si>
+  <si>
+    <t>Acceso a la "Home Page" anónima.</t>
+  </si>
+  <si>
+    <t>Se seleccionarán los cursos de cada categoría y se mostrán en formato de "ficha", 3 por cada categoría.
+Dependiendo del número de cursos encontrados, se mostrará los iconos de "Anterior" (si no es la primera página) y Posterior (si existen más registros y no es la última página).</t>
+  </si>
+  <si>
+    <t>Visualización de cursos existentes.</t>
+  </si>
+  <si>
+    <t>Consulta de Cursos por Áreas</t>
+  </si>
+  <si>
+    <t>Visualización de cursos existentes para el área seleccionada.</t>
+  </si>
+  <si>
+    <t>Se mostrará en pantalla los cursos existentes del área seleccionada forma paginada en 3 categorías:
+1.- Cursos más populares (Cursos con mayor número de vistas)
+2.- Cursos mejor valororados (Cursos ordenados por mejor valoración media)
+3.- Cursos con mayor participación (Cursos ordenados por número de estudiantes inscritos)</t>
+  </si>
+  <si>
+    <t>Selección de Área en el buscador de la Home.</t>
+  </si>
+  <si>
+    <t>Se seleccionarán los cursos de cada categoría filtrados por el área seleccionada y se mostrán en formato de "ficha", 3 por cada categoría.
+Dependiendo del número de cursos encontrados, se mostrará los iconos de "Anterior" (si no es la primera página) y Posterior (si existen más registros y no es la última página).</t>
+  </si>
+  <si>
+    <t>Consuta del Manual</t>
+  </si>
+  <si>
+    <t>Visualización del manual de ayuda al usuario y descripción de la plataforma.</t>
+  </si>
+  <si>
+    <t>Se mostrará en pantalla (nueva ventana), el manual de usuario existente.</t>
+  </si>
+  <si>
+    <t>Selección de la opción "Manual de Ayuda" de la Home.</t>
+  </si>
+  <si>
+    <t>Se abrirá ventana nueva con el contenido del manual de usuario existente.</t>
+  </si>
+  <si>
+    <t>FR_01-004</t>
+  </si>
+  <si>
+    <t>FR_01-003</t>
+  </si>
+  <si>
+    <t>FR_01-002</t>
+  </si>
+  <si>
+    <t>Consulta del Manual</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>FR_01-005</t>
+  </si>
+  <si>
+    <t>Registrarse en la plataforma</t>
+  </si>
+  <si>
+    <t>Darse de alta en la plataforma para acceder a la parte privada.</t>
+  </si>
+  <si>
+    <t>Se mostrará un formulario de datos para registrarse en la plataforma:
+- E-MAIL. Dirección de correo del nuevo estudiante. Será su identificador para acceso a la plataforma.
+- Contraseña. Contraseña a utilizar en el acceso futuro.
+-Confirmar Contraseña. Repetir por seguridad la contraseña introducida.
+- Nombre. Nombre del Estudiante.
+- Primer apellido. Primer apellido del estudiante.
+- Localidad. Localidad de residencia.
+- Provincia. Provincia de residencia.
+- Código postal. Código postal de la residencia.
+- Áreas de Interés. (opcional). Áreas de interes del estudiante para mejorar los resultados de sus búsquedas.</t>
+  </si>
+  <si>
+    <t>Selección de la opción "Registrarse" desde el menú de la "Home" o desde la pantalla de Login</t>
+  </si>
+  <si>
+    <t>Si el usuario existe, se mostrará el mensaje correspondiente.
+Si es correcto se le redirigirá a la pantalla de LOGIN.</t>
+  </si>
+  <si>
+    <t>FR_01-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizar el "Login" </t>
+  </si>
+  <si>
+    <t>Identificación de acceso a la plataforma.</t>
+  </si>
+  <si>
+    <t>Se mostrará un formulario de login.
+- Usuario. Dirección de correo del usuario/estudiante
+- Contraseña. Contraseña del usuario/estudiante.</t>
+  </si>
+  <si>
+    <t>Selección de la opción "Login" desde el menú de la "Home" o desde alguna opción de acceso privado (p.ejmp. Inscribirse a un curso)</t>
+  </si>
+  <si>
+    <t>Si los datos de identificación son correctos, accederá a la "Home" correspondiente (Estudiante/Profesor/Administrador)
+Si los datos son incorrectos (no está en la plataforma), se indicará mediante mensaje "Usuario/Contraseña incorrecta".
+Si el usuario está "bloqueado". Se mostrará el mensaje correspondiente y no podrá acceder a los contenidos privados de la plataforma.</t>
+  </si>
+  <si>
+    <t>FR_01-007</t>
+  </si>
+  <si>
+    <t>Modificar idioma</t>
+  </si>
+  <si>
+    <t>Mostrar los mensajes al usuario en varios idiomas</t>
+  </si>
+  <si>
+    <t>Se mostrará, a través de una opción "desplegable" los diferentes idiomas disponibles en la plataforma. 
+Se dispone de Español y de Inglés.</t>
+  </si>
+  <si>
+    <t>Selección del idioma disponible en la opción que se implemente.</t>
+  </si>
+  <si>
+    <t>Se realiza una recarga de la pantalla actual, mostrándose los textos "fijos" en el idioma seleccionado.</t>
+  </si>
+  <si>
+    <t>Baja</t>
   </si>
 </sst>
 </file>
@@ -587,7 +621,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="4:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="4:5" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="4:5" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D4" s="1" t="s">
         <v>0</v>
       </c>
@@ -600,47 +634,479 @@
         <v>2</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="4:5" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="4:5" ht="123.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="4:5" ht="78" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D7" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="4:5" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D8" s="3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="4:5" ht="135" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D9" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="4:5" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D10" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>13</v>
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C93EFE0C-28F1-4953-AE08-9ACF2B5F3D53}">
+  <dimension ref="D3:E10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="31.7109375" customWidth="1"/>
+    <col min="5" max="5" width="86.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="4:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="4:5" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="4:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="4:5" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="4:5" ht="123.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="4:5" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="4:5" ht="135" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="4:5" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04C93ECC-CE34-41BB-AACB-0C31E3EF4E64}">
+  <dimension ref="D3:E10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="31.7109375" customWidth="1"/>
+    <col min="5" max="5" width="86.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="4:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="4:5" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="4:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="4:5" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="4:5" ht="123.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="4:5" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="4:5" ht="135" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="4:5" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9091308E-7738-493A-BC3C-06BD3BE2CA49}">
+  <dimension ref="D3:E10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="31.7109375" customWidth="1"/>
+    <col min="5" max="5" width="86.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="4:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="4:5" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="4:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="4:5" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="4:5" ht="123.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="4:5" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="4:5" ht="135" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="4:5" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1655EFAD-DBE2-407E-8C96-062D4369775A}">
+  <dimension ref="D3:E10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="31.7109375" customWidth="1"/>
+    <col min="5" max="5" width="86.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="4:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="4:5" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="4:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="4:5" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="4:5" ht="234.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="4:5" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="4:5" ht="135" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="4:5" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54E096D8-491F-4E13-88CA-5F5006BE9E99}">
+  <dimension ref="D3:E10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="31.7109375" customWidth="1"/>
+    <col min="5" max="5" width="86.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="4:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="4:5" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="4:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="4:5" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="4:5" ht="54.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="4:5" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="4:5" ht="135" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="4:5" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72683E51-3849-4E17-B503-821067C149B5}">
+  <dimension ref="D3:E10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="31.7109375" customWidth="1"/>
+    <col min="5" max="5" width="86.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="4:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="4:5" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="4:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="4:5" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="4:5" ht="54.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="4:5" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="4:5" ht="135" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="4:5" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
